--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05608</v>
+        <v>0.047935</v>
       </c>
       <c r="C2" t="n">
-        <v>0.060877</v>
+        <v>0.052023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000975</v>
+        <v>0.000692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003822</v>
+        <v>0.003395</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.337412</v>
+        <v>0.259082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.366273</v>
+        <v>0.281174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005867</v>
+        <v>0.00374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022995</v>
+        <v>0.018352</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.526157</v>
+        <v>0.305454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.571163</v>
+        <v>0.3315</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009148</v>
+        <v>0.00441</v>
       </c>
       <c r="E4" t="n">
-        <v>0.035857</v>
+        <v>0.021636</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.047935</v>
+        <v>0.050011</v>
       </c>
       <c r="C2" t="n">
-        <v>0.052023</v>
+        <v>0.054172</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000692</v>
+        <v>0.000695</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003395</v>
+        <v>0.003467</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.259082</v>
+        <v>0.243554</v>
       </c>
       <c r="C3" t="n">
-        <v>0.281174</v>
+        <v>0.263819</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00374</v>
+        <v>0.003383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.018352</v>
+        <v>0.016882</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.305454</v>
+        <v>0.310539</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3315</v>
+        <v>0.336378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00441</v>
+        <v>0.004313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021636</v>
+        <v>0.021525</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.050011</v>
+        <v>0.050886</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054172</v>
+        <v>0.054976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000695</v>
+        <v>0.000891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003467</v>
+        <v>0.003199</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.243554</v>
+        <v>0.300346</v>
       </c>
       <c r="C3" t="n">
-        <v>0.263819</v>
+        <v>0.324485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003383</v>
+        <v>0.005257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.016882</v>
+        <v>0.018881</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.310539</v>
+        <v>0.343367</v>
       </c>
       <c r="C4" t="n">
-        <v>0.336378</v>
+        <v>0.370963</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004313</v>
+        <v>0.00601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021525</v>
+        <v>0.021585</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.050886</v>
+        <v>0.049558</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054976</v>
+        <v>0.053576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000891</v>
+        <v>0.000922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003199</v>
+        <v>0.003096</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.300346</v>
+        <v>0.297544</v>
       </c>
       <c r="C3" t="n">
-        <v>0.324485</v>
+        <v>0.321665</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005257</v>
+        <v>0.005533</v>
       </c>
       <c r="E3" t="n">
-        <v>0.018881</v>
+        <v>0.018588</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.343367</v>
+        <v>0.341237</v>
       </c>
       <c r="C4" t="n">
-        <v>0.370963</v>
+        <v>0.3689</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00601</v>
+        <v>0.006346</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021585</v>
+        <v>0.021318</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.049558</v>
+        <v>0.045898</v>
       </c>
       <c r="C2" t="n">
-        <v>0.053576</v>
+        <v>0.049502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000922</v>
+        <v>0.000871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003096</v>
+        <v>0.002732</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.297544</v>
+        <v>0.226183</v>
       </c>
       <c r="C3" t="n">
-        <v>0.321665</v>
+        <v>0.243942</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005533</v>
+        <v>0.004293</v>
       </c>
       <c r="E3" t="n">
-        <v>0.018588</v>
+        <v>0.013466</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.341237</v>
+        <v>0.280208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3689</v>
+        <v>0.302208</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006346</v>
+        <v>0.005319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021318</v>
+        <v>0.016682</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.045898</v>
+        <v>0.045557</v>
       </c>
       <c r="C2" t="n">
-        <v>0.049502</v>
+        <v>0.049217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000871</v>
+        <v>0.001268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002732</v>
+        <v>0.002392</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.226183</v>
+        <v>0.210785</v>
       </c>
       <c r="C3" t="n">
-        <v>0.243942</v>
+        <v>0.227718</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004293</v>
+        <v>0.005868</v>
       </c>
       <c r="E3" t="n">
-        <v>0.013466</v>
+        <v>0.011065</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.280208</v>
+        <v>0.253831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.302208</v>
+        <v>0.274223</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005319</v>
+        <v>0.007066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016682</v>
+        <v>0.013325</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.045557</v>
+        <v>0.045842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.049217</v>
+        <v>0.049535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001268</v>
+        <v>0.001243</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002392</v>
+        <v>0.00245</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.210785</v>
+        <v>0.211738</v>
       </c>
       <c r="C3" t="n">
-        <v>0.227718</v>
+        <v>0.228795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005868</v>
+        <v>0.005742</v>
       </c>
       <c r="E3" t="n">
-        <v>0.011065</v>
+        <v>0.011316</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.253831</v>
+        <v>0.25523</v>
       </c>
       <c r="C4" t="n">
-        <v>0.274223</v>
+        <v>0.275792</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007066</v>
+        <v>0.006921</v>
       </c>
       <c r="E4" t="n">
-        <v>0.013325</v>
+        <v>0.01364</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.045842</v>
+        <v>0.048184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.049535</v>
+        <v>0.051278</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001243</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00245</v>
+        <v>0.003094</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.211738</v>
+        <v>0.229919</v>
       </c>
       <c r="C3" t="n">
-        <v>0.228795</v>
+        <v>0.244684</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005742</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.011316</v>
+        <v>0.014765</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25523</v>
+        <v>0.260714</v>
       </c>
       <c r="C4" t="n">
-        <v>0.275792</v>
+        <v>0.277456</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006921</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01364</v>
+        <v>0.016742</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048184</v>
+        <v>0.048049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051278</v>
+        <v>0.051098</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003094</v>
+        <v>0.003049</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.229919</v>
+        <v>0.229012</v>
       </c>
       <c r="C3" t="n">
-        <v>0.244684</v>
+        <v>0.243544</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.014765</v>
+        <v>0.014532</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.260714</v>
+        <v>0.258875</v>
       </c>
       <c r="C4" t="n">
-        <v>0.277456</v>
+        <v>0.275302</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016742</v>
+        <v>0.016427</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048049</v>
+        <v>0.04813</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051098</v>
+        <v>0.051049</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003049</v>
+        <v>0.002919</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.229012</v>
+        <v>0.227431</v>
       </c>
       <c r="C3" t="n">
-        <v>0.243544</v>
+        <v>0.241226</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.014532</v>
+        <v>0.013795</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.258875</v>
+        <v>0.257426</v>
       </c>
       <c r="C4" t="n">
-        <v>0.275302</v>
+        <v>0.273041</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016427</v>
+        <v>0.015614</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04813</v>
+        <v>0.04833</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051049</v>
+        <v>0.051156</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002919</v>
+        <v>0.002826</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.227431</v>
+        <v>0.225764</v>
       </c>
       <c r="C3" t="n">
-        <v>0.241226</v>
+        <v>0.238965</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.013795</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.257426</v>
+        <v>0.258349</v>
       </c>
       <c r="C4" t="n">
-        <v>0.273041</v>
+        <v>0.273454</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015614</v>
+        <v>0.015106</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04833</v>
+        <v>0.048376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051156</v>
+        <v>0.051161</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002826</v>
+        <v>0.002786</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.225764</v>
+        <v>0.225119</v>
       </c>
       <c r="C3" t="n">
-        <v>0.238965</v>
+        <v>0.238082</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0132</v>
+        <v>0.012963</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.258349</v>
+        <v>0.258728</v>
       </c>
       <c r="C4" t="n">
-        <v>0.273454</v>
+        <v>0.273627</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015106</v>
+        <v>0.014898</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048376</v>
+        <v>0.048505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051161</v>
+        <v>0.050998</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002786</v>
+        <v>0.002493</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.225119</v>
+        <v>0.234258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.238082</v>
+        <v>0.246299</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.012963</v>
+        <v>0.01204</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.258728</v>
+        <v>0.293574</v>
       </c>
       <c r="C4" t="n">
-        <v>0.273627</v>
+        <v>0.308663</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.014898</v>
+        <v>0.015089</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048505</v>
+        <v>0.0485</v>
       </c>
       <c r="C2" t="n">
-        <v>0.050998</v>
+        <v>0.051004</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002493</v>
+        <v>0.002504</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.234258</v>
+        <v>0.234331</v>
       </c>
       <c r="C3" t="n">
-        <v>0.246299</v>
+        <v>0.246428</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01204</v>
+        <v>0.012097</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.293574</v>
+        <v>0.293547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015089</v>
+        <v>0.015153</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0485</v>
+        <v>0.048185</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051004</v>
+        <v>0.050595</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002504</v>
+        <v>0.00241</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.234331</v>
+        <v>0.237935</v>
       </c>
       <c r="C3" t="n">
-        <v>0.246428</v>
+        <v>0.249837</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.012097</v>
+        <v>0.011902</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.293547</v>
+        <v>0.297704</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015153</v>
+        <v>0.014891</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048185</v>
+        <v>0.048499</v>
       </c>
       <c r="C2" t="n">
-        <v>0.050595</v>
+        <v>0.050924</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00241</v>
+        <v>0.002425</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.237935</v>
+        <v>0.23821</v>
       </c>
       <c r="C3" t="n">
-        <v>0.249837</v>
+        <v>0.250119</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.011902</v>
+        <v>0.01191</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
       <c r="C4" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.014891</v>
+        <v>0.014898</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/decomposition_summary.xlsx
+++ b/vignettes/vignette-2/decomposition_summary.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.048499</v>
+        <v>0.04819</v>
       </c>
       <c r="C2" t="n">
-        <v>0.050924</v>
+        <v>0.050632</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002425</v>
+        <v>0.002442</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.23821</v>
+        <v>0.245853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.250119</v>
+        <v>0.258309</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01191</v>
+        <v>0.012456</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.297977</v>
+        <v>0.304954</v>
       </c>
       <c r="C4" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.014898</v>
+        <v>0.015451</v>
       </c>
     </row>
   </sheetData>
